--- a/artfynd/A 32973-2025 artfynd.xlsx
+++ b/artfynd/A 32973-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,210 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126401749</v>
+      </c>
+      <c r="B3" t="n">
+        <v>55950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>206178</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lake</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lota lota</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Torestorpsån, bron ovan övermån, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>361754</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6363258</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torestorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1984-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1984-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Elfiske fr Lst, gammal artuppgift, inlagd av Marks Kommun</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126401743</v>
+      </c>
+      <c r="B4" t="n">
+        <v>55440</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206063</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anguilla anguilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Torestorpsån, bron ovan övermån, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>361754</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6363258</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torestorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1984-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1984-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Elfiske fr Lst, gammal artuppgift, inlagd av Marks Kommun</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32973-2025 artfynd.xlsx
+++ b/artfynd/A 32973-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>126401749</v>
       </c>
       <c r="B3" t="n">
-        <v>55950</v>
+        <v>55951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>126401743</v>
       </c>
       <c r="B4" t="n">
-        <v>55440</v>
+        <v>55441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
